--- a/템플릿/국가철도50억미만_템플릿.xlsx
+++ b/템플릿/국가철도50억미만_템플릿.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\템플릿\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ihwijae\Desktop\템플릿\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1632,6 +1632,102 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="41" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1641,6 +1737,12 @@
     <xf numFmtId="41" fontId="4" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1648,108 +1750,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="16" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="16" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2102,53 +2102,53 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="151">
+      <c r="D1" s="183">
         <v>2</v>
       </c>
-      <c r="E1" s="151"/>
-      <c r="F1" s="152"/>
-      <c r="G1" s="153"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="185"/>
       <c r="H1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="151">
+      <c r="I1" s="183">
         <f>D2</f>
         <v>0</v>
       </c>
-      <c r="J1" s="151"/>
+      <c r="J1" s="183"/>
       <c r="K1" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="154"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="155" t="s">
+      <c r="L1" s="188"/>
+      <c r="M1" s="188"/>
+      <c r="N1" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="156"/>
-      <c r="T1" s="156"/>
-      <c r="U1" s="156"/>
-      <c r="V1" s="156"/>
-      <c r="W1" s="156"/>
-      <c r="X1" s="156"/>
-      <c r="Y1" s="156"/>
-      <c r="Z1" s="156"/>
-      <c r="AA1" s="156"/>
-      <c r="AB1" s="156"/>
+      <c r="O1" s="190"/>
+      <c r="P1" s="190"/>
+      <c r="Q1" s="190"/>
+      <c r="R1" s="190"/>
+      <c r="S1" s="190"/>
+      <c r="T1" s="190"/>
+      <c r="U1" s="190"/>
+      <c r="V1" s="190"/>
+      <c r="W1" s="190"/>
+      <c r="X1" s="190"/>
+      <c r="Y1" s="190"/>
+      <c r="Z1" s="190"/>
+      <c r="AA1" s="190"/>
+      <c r="AB1" s="190"/>
       <c r="AC1" s="133"/>
-      <c r="AD1" s="173" t="s">
+      <c r="AD1" s="154" t="s">
         <v>50</v>
       </c>
-      <c r="AE1" s="173"/>
-      <c r="AF1" s="173"/>
-      <c r="AG1" s="173"/>
-      <c r="AH1" s="173"/>
-      <c r="AI1" s="173"/>
-      <c r="AJ1" s="173"/>
-      <c r="AK1" s="173"/>
+      <c r="AE1" s="154"/>
+      <c r="AF1" s="154"/>
+      <c r="AG1" s="154"/>
+      <c r="AH1" s="154"/>
+      <c r="AI1" s="154"/>
+      <c r="AJ1" s="154"/>
+      <c r="AK1" s="154"/>
       <c r="AL1" s="80"/>
       <c r="AM1" s="80"/>
       <c r="AN1" s="80"/>
@@ -2166,18 +2166,18 @@
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="153"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="185"/>
       <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="171">
+      <c r="I2" s="186">
         <f>I1</f>
         <v>0</v>
       </c>
-      <c r="J2" s="171"/>
+      <c r="J2" s="186"/>
       <c r="K2" s="73" t="s">
         <v>11</v>
       </c>
@@ -2187,28 +2187,28 @@
       <c r="O2" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="172"/>
-      <c r="Q2" s="172"/>
-      <c r="R2" s="172"/>
-      <c r="S2" s="172"/>
+      <c r="P2" s="187"/>
+      <c r="Q2" s="187"/>
+      <c r="R2" s="187"/>
+      <c r="S2" s="187"/>
       <c r="T2" s="84"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="157"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="157"/>
-      <c r="Y2" s="157"/>
-      <c r="Z2" s="157"/>
+      <c r="U2" s="172"/>
+      <c r="V2" s="172"/>
+      <c r="W2" s="172"/>
+      <c r="X2" s="172"/>
+      <c r="Y2" s="172"/>
+      <c r="Z2" s="172"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5"/>
       <c r="AC2" s="115"/>
-      <c r="AD2" s="174"/>
-      <c r="AE2" s="174"/>
-      <c r="AF2" s="174"/>
-      <c r="AG2" s="174"/>
-      <c r="AH2" s="174"/>
-      <c r="AI2" s="174"/>
-      <c r="AJ2" s="174"/>
-      <c r="AK2" s="174"/>
+      <c r="AD2" s="155"/>
+      <c r="AE2" s="155"/>
+      <c r="AF2" s="155"/>
+      <c r="AG2" s="155"/>
+      <c r="AH2" s="155"/>
+      <c r="AI2" s="155"/>
+      <c r="AJ2" s="155"/>
+      <c r="AK2" s="155"/>
       <c r="AL2" s="138"/>
       <c r="AM2" s="5"/>
       <c r="AN2" s="5"/>
@@ -2232,60 +2232,60 @@
       <c r="BB2" s="107"/>
     </row>
     <row r="3" spans="1:54" s="12" customFormat="1" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A3" s="158" t="s">
+      <c r="A3" s="173" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="158" t="s">
+      <c r="B3" s="173" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="160" t="s">
+      <c r="C3" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="161"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="162"/>
-      <c r="G3" s="162"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="160" t="s">
+      <c r="D3" s="170"/>
+      <c r="E3" s="170"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="176"/>
+      <c r="I3" s="169" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="161"/>
-      <c r="K3" s="161"/>
-      <c r="L3" s="164"/>
-      <c r="M3" s="165"/>
-      <c r="N3" s="166" t="s">
+      <c r="J3" s="170"/>
+      <c r="K3" s="170"/>
+      <c r="L3" s="177"/>
+      <c r="M3" s="178"/>
+      <c r="N3" s="179" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="168" t="s">
+      <c r="O3" s="181" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="160" t="s">
+      <c r="P3" s="169" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="161"/>
-      <c r="R3" s="161"/>
-      <c r="S3" s="161"/>
-      <c r="T3" s="161"/>
-      <c r="U3" s="170"/>
+      <c r="Q3" s="170"/>
+      <c r="R3" s="170"/>
+      <c r="S3" s="170"/>
+      <c r="T3" s="170"/>
+      <c r="U3" s="171"/>
       <c r="V3" s="11"/>
-      <c r="W3" s="160" t="s">
+      <c r="W3" s="169" t="s">
         <v>19</v>
       </c>
-      <c r="X3" s="161"/>
-      <c r="Y3" s="161"/>
-      <c r="Z3" s="161"/>
-      <c r="AA3" s="161"/>
-      <c r="AB3" s="162"/>
+      <c r="X3" s="170"/>
+      <c r="Y3" s="170"/>
+      <c r="Z3" s="170"/>
+      <c r="AA3" s="170"/>
+      <c r="AB3" s="175"/>
       <c r="AC3" s="150"/>
-      <c r="AD3" s="160" t="s">
+      <c r="AD3" s="169" t="s">
         <v>20</v>
       </c>
-      <c r="AE3" s="161"/>
-      <c r="AF3" s="161"/>
-      <c r="AG3" s="161"/>
-      <c r="AH3" s="161"/>
-      <c r="AI3" s="161"/>
-      <c r="AJ3" s="170"/>
+      <c r="AE3" s="170"/>
+      <c r="AF3" s="170"/>
+      <c r="AG3" s="170"/>
+      <c r="AH3" s="170"/>
+      <c r="AI3" s="170"/>
+      <c r="AJ3" s="171"/>
       <c r="AK3" s="148" t="s">
         <v>21</v>
       </c>
@@ -2293,49 +2293,49 @@
       <c r="AM3" s="149"/>
       <c r="AN3" s="149"/>
       <c r="AO3" s="79"/>
-      <c r="AP3" s="178" t="s">
+      <c r="AP3" s="159" t="s">
         <v>22</v>
       </c>
-      <c r="AQ3" s="180" t="s">
+      <c r="AQ3" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="AR3" s="182" t="s">
+      <c r="AR3" s="163" t="s">
         <v>24</v>
       </c>
-      <c r="AS3" s="184" t="s">
+      <c r="AS3" s="165" t="s">
         <v>25</v>
       </c>
-      <c r="AT3" s="186" t="s">
+      <c r="AT3" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="AU3" s="176" t="s">
+      <c r="AU3" s="157" t="s">
         <v>27</v>
       </c>
-      <c r="AV3" s="175" t="s">
+      <c r="AV3" s="156" t="s">
         <v>28</v>
       </c>
-      <c r="AW3" s="175" t="s">
+      <c r="AW3" s="156" t="s">
         <v>29</v>
       </c>
-      <c r="AX3" s="175" t="s">
+      <c r="AX3" s="156" t="s">
         <v>30</v>
       </c>
-      <c r="AY3" s="175" t="s">
+      <c r="AY3" s="156" t="s">
         <v>31</v>
       </c>
-      <c r="AZ3" s="175" t="s">
+      <c r="AZ3" s="156" t="s">
         <v>32</v>
       </c>
-      <c r="BA3" s="175" t="s">
+      <c r="BA3" s="156" t="s">
         <v>33</v>
       </c>
-      <c r="BB3" s="175" t="s">
+      <c r="BB3" s="156" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:54" s="12" customFormat="1" ht="39.75" customHeight="1" thickBot="1">
-      <c r="A4" s="159"/>
-      <c r="B4" s="159"/>
+      <c r="A4" s="174"/>
+      <c r="B4" s="174"/>
       <c r="C4" s="30" t="s">
         <v>6</v>
       </c>
@@ -2369,8 +2369,8 @@
       <c r="M4" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="167"/>
-      <c r="O4" s="169"/>
+      <c r="N4" s="180"/>
+      <c r="O4" s="182"/>
       <c r="P4" s="30" t="s">
         <v>6</v>
       </c>
@@ -2449,19 +2449,19 @@
       <c r="AO4" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="AP4" s="179"/>
-      <c r="AQ4" s="181"/>
-      <c r="AR4" s="183"/>
-      <c r="AS4" s="185"/>
-      <c r="AT4" s="187"/>
-      <c r="AU4" s="177"/>
-      <c r="AV4" s="175"/>
-      <c r="AW4" s="175"/>
-      <c r="AX4" s="175"/>
-      <c r="AY4" s="175"/>
-      <c r="AZ4" s="175"/>
-      <c r="BA4" s="175"/>
-      <c r="BB4" s="175"/>
+      <c r="AP4" s="160"/>
+      <c r="AQ4" s="162"/>
+      <c r="AR4" s="164"/>
+      <c r="AS4" s="166"/>
+      <c r="AT4" s="168"/>
+      <c r="AU4" s="158"/>
+      <c r="AV4" s="156"/>
+      <c r="AW4" s="156"/>
+      <c r="AX4" s="156"/>
+      <c r="AY4" s="156"/>
+      <c r="AZ4" s="156"/>
+      <c r="BA4" s="156"/>
+      <c r="BB4" s="156"/>
     </row>
     <row r="5" spans="1:54" s="12" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="A5" s="122"/>
@@ -2520,23 +2520,24 @@
         <v>0</v>
       </c>
       <c r="AJ5" s="92">
-        <v>5</v>
+        <f t="shared" ref="AJ5:AJ53" si="6">IF(AI5&gt;=2,5,IF(AI5&gt;=1.5,4,IF(AI5&gt;=0.75,3,0)))</f>
+        <v>0</v>
       </c>
       <c r="AK5" s="94"/>
       <c r="AL5" s="97"/>
       <c r="AM5" s="34" t="e">
-        <f t="shared" ref="AM5:AM53" si="6">IF((V5+AC5+AJ5+AK5)&gt;=30,30,(V5+AC5+AJ5+AK5))</f>
+        <f t="shared" ref="AM5:AM53" si="7">IF((V5+AC5+AJ5+AK5)&gt;=30,30,(V5+AC5+AJ5+AK5))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AN5" s="48">
         <v>65</v>
       </c>
       <c r="AO5" s="49" t="e">
-        <f t="shared" ref="AO5:AO53" si="7">AN5+AM5+AL5</f>
+        <f t="shared" ref="AO5:AO53" si="8">AN5+AM5+AL5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AP5" s="50" t="e">
-        <f t="shared" ref="AP5:AP35" si="8">-((70-((264+(65+(30-AM5)))))/300)</f>
+        <f t="shared" ref="AP5:AP35" si="9">-((70-((264+(65+(30-AM5)))))/300)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ5" s="51"/>
@@ -2544,11 +2545,11 @@
         <v>0</v>
       </c>
       <c r="AS5" s="36">
-        <f t="shared" ref="AS5:AS35" si="9">100%+AR5</f>
+        <f t="shared" ref="AS5:AS35" si="10">100%+AR5</f>
         <v>1</v>
       </c>
       <c r="AT5" s="26" t="e">
-        <f t="shared" ref="AT5:AT35" si="10">ROUNDUP($D$2*AP5*AS5,-3)</f>
+        <f t="shared" ref="AT5:AT35" si="11">ROUNDUP($D$2*AP5*AS5,-3)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AU5" s="27"/>
@@ -2558,11 +2559,11 @@
       <c r="AY5" s="104"/>
       <c r="AZ5" s="105"/>
       <c r="BA5" s="105">
-        <f t="shared" ref="BA5:BA53" si="11">AV5+AW5+AX5+AY5+AZ5</f>
+        <f t="shared" ref="BA5:BA53" si="12">AV5+AW5+AX5+AY5+AZ5</f>
         <v>0</v>
       </c>
       <c r="BB5" s="106">
-        <f t="shared" ref="BB5:BB53" si="12">(AV5*I5)+(AW5*J5)+(AX5*K5)+(AY5*L5)+(AZ5*M5)</f>
+        <f t="shared" ref="BB5:BB53" si="13">(AV5*I5)+(AW5*J5)+(AX5*K5)+(AY5*L5)+(AZ5*M5)</f>
         <v>0</v>
       </c>
     </row>
@@ -2573,7 +2574,7 @@
       <c r="D6" s="130"/>
       <c r="E6" s="130"/>
       <c r="F6" s="128"/>
-      <c r="G6" s="188"/>
+      <c r="G6" s="151"/>
       <c r="H6" s="129"/>
       <c r="I6" s="126"/>
       <c r="J6" s="39"/>
@@ -2623,23 +2624,24 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="92">
-        <v>5</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AK6" s="94"/>
       <c r="AL6" s="97"/>
       <c r="AM6" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN6" s="48">
         <v>65</v>
       </c>
       <c r="AO6" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP6" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ6" s="51"/>
@@ -2647,11 +2649,11 @@
         <v>0</v>
       </c>
       <c r="AS6" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT6" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU6" s="27"/>
@@ -2661,11 +2663,11 @@
       <c r="AY6" s="104"/>
       <c r="AZ6" s="105"/>
       <c r="BA6" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB6" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2676,7 +2678,7 @@
       <c r="D7" s="131"/>
       <c r="E7" s="131"/>
       <c r="F7" s="124"/>
-      <c r="G7" s="188"/>
+      <c r="G7" s="151"/>
       <c r="H7" s="144"/>
       <c r="I7" s="132"/>
       <c r="J7" s="39"/>
@@ -2684,7 +2686,7 @@
       <c r="L7" s="39"/>
       <c r="M7" s="45"/>
       <c r="N7" s="41">
-        <f t="shared" ref="N7:N53" si="13">SUM(I7:L7)</f>
+        <f t="shared" ref="N7:N53" si="14">SUM(I7:L7)</f>
         <v>0</v>
       </c>
       <c r="O7" s="47">
@@ -2726,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="AJ7" s="92">
-        <f t="shared" ref="AJ7:AJ53" si="14">IF(AI7&gt;=2,5,IF(AI7&gt;=1.5,4,IF(AI7&gt;=0.75,3,0)))</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK7" s="94">
@@ -2735,18 +2737,18 @@
       </c>
       <c r="AL7" s="97"/>
       <c r="AM7" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN7" s="48">
         <v>65</v>
       </c>
       <c r="AO7" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP7" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ7" s="51"/>
@@ -2754,11 +2756,11 @@
         <v>0</v>
       </c>
       <c r="AS7" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT7" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU7" s="27"/>
@@ -2768,11 +2770,11 @@
       <c r="AY7" s="104"/>
       <c r="AZ7" s="105"/>
       <c r="BA7" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB7" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2783,7 +2785,7 @@
       <c r="D8" s="130"/>
       <c r="E8" s="130"/>
       <c r="F8" s="124"/>
-      <c r="G8" s="189"/>
+      <c r="G8" s="152"/>
       <c r="H8" s="129"/>
       <c r="I8" s="126"/>
       <c r="J8" s="39"/>
@@ -2833,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK8" s="94">
@@ -2842,18 +2844,18 @@
       </c>
       <c r="AL8" s="97"/>
       <c r="AM8" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN8" s="48">
         <v>65</v>
       </c>
       <c r="AO8" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP8" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ8" s="51"/>
@@ -2861,11 +2863,11 @@
         <v>0</v>
       </c>
       <c r="AS8" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT8" s="88" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU8" s="89"/>
@@ -2875,11 +2877,11 @@
       <c r="AY8" s="104"/>
       <c r="AZ8" s="105"/>
       <c r="BA8" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB8" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -2898,7 +2900,7 @@
       <c r="L9" s="39"/>
       <c r="M9" s="45"/>
       <c r="N9" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O9" s="47">
@@ -2940,24 +2942,24 @@
         <v>0</v>
       </c>
       <c r="AJ9" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK9" s="94"/>
       <c r="AL9" s="97"/>
       <c r="AM9" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN9" s="48">
         <v>65</v>
       </c>
       <c r="AO9" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP9" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ9" s="51"/>
@@ -2965,11 +2967,11 @@
         <v>0</v>
       </c>
       <c r="AS9" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT9" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU9" s="27"/>
@@ -2979,11 +2981,11 @@
       <c r="AY9" s="104"/>
       <c r="AZ9" s="105"/>
       <c r="BA9" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB9" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -3002,7 +3004,7 @@
       <c r="L10" s="39"/>
       <c r="M10" s="45"/>
       <c r="N10" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O10" s="47">
@@ -3046,24 +3048,24 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK10" s="94"/>
       <c r="AL10" s="97"/>
       <c r="AM10" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN10" s="48">
         <v>65</v>
       </c>
       <c r="AO10" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP10" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ10" s="51"/>
@@ -3071,11 +3073,11 @@
         <v>0</v>
       </c>
       <c r="AS10" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT10" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU10" s="27"/>
@@ -3085,11 +3087,11 @@
       <c r="AY10" s="104"/>
       <c r="AZ10" s="105"/>
       <c r="BA10" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB10" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -3100,7 +3102,7 @@
       <c r="D11" s="131"/>
       <c r="E11" s="124"/>
       <c r="F11" s="124"/>
-      <c r="G11" s="188"/>
+      <c r="G11" s="151"/>
       <c r="H11" s="52"/>
       <c r="I11" s="126"/>
       <c r="J11" s="39"/>
@@ -3108,7 +3110,7 @@
       <c r="L11" s="39"/>
       <c r="M11" s="45"/>
       <c r="N11" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O11" s="47">
@@ -3150,24 +3152,24 @@
         <v>0</v>
       </c>
       <c r="AJ11" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK11" s="94"/>
       <c r="AL11" s="97"/>
       <c r="AM11" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN11" s="48">
         <v>65</v>
       </c>
       <c r="AO11" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP11" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ11" s="51"/>
@@ -3175,11 +3177,11 @@
         <v>0</v>
       </c>
       <c r="AS11" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT11" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU11" s="27"/>
@@ -3189,11 +3191,11 @@
       <c r="AY11" s="104"/>
       <c r="AZ11" s="105"/>
       <c r="BA11" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB11" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -3204,7 +3206,7 @@
       <c r="D12" s="131"/>
       <c r="E12" s="124"/>
       <c r="F12" s="124"/>
-      <c r="G12" s="188"/>
+      <c r="G12" s="151"/>
       <c r="H12" s="129"/>
       <c r="I12" s="126"/>
       <c r="J12" s="39"/>
@@ -3212,7 +3214,7 @@
       <c r="L12" s="39"/>
       <c r="M12" s="45"/>
       <c r="N12" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O12" s="19">
@@ -3254,24 +3256,24 @@
         <v>0</v>
       </c>
       <c r="AJ12" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK12" s="94"/>
       <c r="AL12" s="97"/>
       <c r="AM12" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN12" s="48">
         <v>65</v>
       </c>
       <c r="AO12" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP12" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ12" s="51"/>
@@ -3279,11 +3281,11 @@
         <v>0</v>
       </c>
       <c r="AS12" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT12" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU12" s="27"/>
@@ -3293,11 +3295,11 @@
       <c r="AY12" s="104"/>
       <c r="AZ12" s="105"/>
       <c r="BA12" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB12" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -3316,7 +3318,7 @@
       <c r="L13" s="39"/>
       <c r="M13" s="45"/>
       <c r="N13" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O13" s="19">
@@ -3358,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="AJ13" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK13" s="94">
@@ -3367,28 +3369,28 @@
       </c>
       <c r="AL13" s="97"/>
       <c r="AM13" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN13" s="48">
         <v>65</v>
       </c>
       <c r="AO13" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP13" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ13" s="51"/>
       <c r="AR13" s="35"/>
       <c r="AS13" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT13" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU13" s="27"/>
@@ -3398,11 +3400,11 @@
       <c r="AY13" s="104"/>
       <c r="AZ13" s="105"/>
       <c r="BA13" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB13" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -3413,7 +3415,7 @@
       <c r="D14" s="124"/>
       <c r="E14" s="124"/>
       <c r="F14" s="124"/>
-      <c r="G14" s="188"/>
+      <c r="G14" s="151"/>
       <c r="H14" s="52"/>
       <c r="I14" s="126"/>
       <c r="J14" s="39"/>
@@ -3421,7 +3423,7 @@
       <c r="L14" s="39"/>
       <c r="M14" s="45"/>
       <c r="N14" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O14" s="19">
@@ -3463,24 +3465,24 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK14" s="94"/>
       <c r="AL14" s="97"/>
       <c r="AM14" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN14" s="48">
         <v>65</v>
       </c>
       <c r="AO14" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP14" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ14" s="51"/>
@@ -3488,11 +3490,11 @@
         <v>0</v>
       </c>
       <c r="AS14" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT14" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU14" s="27"/>
@@ -3502,11 +3504,11 @@
       <c r="AY14" s="104"/>
       <c r="AZ14" s="105"/>
       <c r="BA14" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB14" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -3517,7 +3519,7 @@
       <c r="D15" s="124"/>
       <c r="E15" s="124"/>
       <c r="F15" s="124"/>
-      <c r="G15" s="188"/>
+      <c r="G15" s="151"/>
       <c r="H15" s="52"/>
       <c r="I15" s="112"/>
       <c r="J15" s="39"/>
@@ -3525,7 +3527,7 @@
       <c r="L15" s="39"/>
       <c r="M15" s="45"/>
       <c r="N15" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O15" s="19">
@@ -3569,34 +3571,34 @@
         <v>0</v>
       </c>
       <c r="AJ15" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK15" s="94"/>
       <c r="AL15" s="97"/>
       <c r="AM15" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN15" s="48">
         <v>65</v>
       </c>
       <c r="AO15" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP15" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ15" s="51"/>
       <c r="AR15" s="35"/>
       <c r="AS15" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT15" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU15" s="27"/>
@@ -3606,11 +3608,11 @@
       <c r="AY15" s="104"/>
       <c r="AZ15" s="105"/>
       <c r="BA15" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB15" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -3629,7 +3631,7 @@
       <c r="L16" s="39"/>
       <c r="M16" s="45"/>
       <c r="N16" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O16" s="19">
@@ -3671,24 +3673,24 @@
         <v>0</v>
       </c>
       <c r="AJ16" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK16" s="94"/>
       <c r="AL16" s="97"/>
       <c r="AM16" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN16" s="48">
         <v>65</v>
       </c>
       <c r="AO16" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP16" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ16" s="51"/>
@@ -3696,11 +3698,11 @@
         <v>0</v>
       </c>
       <c r="AS16" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT16" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU16" s="27"/>
@@ -3710,18 +3712,18 @@
       <c r="AY16" s="104"/>
       <c r="AZ16" s="105"/>
       <c r="BA16" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB16" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:54" s="12" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
       <c r="A17" s="32"/>
       <c r="B17" s="143"/>
-      <c r="C17" s="190"/>
+      <c r="C17" s="153"/>
       <c r="D17" s="143"/>
       <c r="E17" s="124"/>
       <c r="F17" s="124"/>
@@ -3733,7 +3735,7 @@
       <c r="L17" s="39"/>
       <c r="M17" s="45"/>
       <c r="N17" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O17" s="19">
@@ -3775,24 +3777,24 @@
         <v>0</v>
       </c>
       <c r="AJ17" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK17" s="94"/>
       <c r="AL17" s="97"/>
       <c r="AM17" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN17" s="48">
         <v>65</v>
       </c>
       <c r="AO17" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP17" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ17" s="51"/>
@@ -3800,11 +3802,11 @@
         <v>0</v>
       </c>
       <c r="AS17" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT17" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU17" s="27"/>
@@ -3814,11 +3816,11 @@
       <c r="AY17" s="104"/>
       <c r="AZ17" s="105"/>
       <c r="BA17" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB17" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -3837,7 +3839,7 @@
       <c r="L18" s="39"/>
       <c r="M18" s="45"/>
       <c r="N18" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O18" s="19">
@@ -3879,24 +3881,24 @@
         <v>0</v>
       </c>
       <c r="AJ18" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK18" s="94"/>
       <c r="AL18" s="97"/>
       <c r="AM18" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN18" s="48">
         <v>65</v>
       </c>
       <c r="AO18" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP18" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ18" s="51"/>
@@ -3904,11 +3906,11 @@
         <v>0</v>
       </c>
       <c r="AS18" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT18" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU18" s="27"/>
@@ -3918,11 +3920,11 @@
       <c r="AY18" s="104"/>
       <c r="AZ18" s="105"/>
       <c r="BA18" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB18" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -3941,7 +3943,7 @@
       <c r="L19" s="39"/>
       <c r="M19" s="45"/>
       <c r="N19" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O19" s="19">
@@ -3983,24 +3985,24 @@
         <v>0</v>
       </c>
       <c r="AJ19" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK19" s="94"/>
       <c r="AL19" s="97"/>
       <c r="AM19" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN19" s="48">
         <v>65</v>
       </c>
       <c r="AO19" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP19" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ19" s="51"/>
@@ -4008,11 +4010,11 @@
         <v>0</v>
       </c>
       <c r="AS19" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT19" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU19" s="27"/>
@@ -4022,11 +4024,11 @@
       <c r="AY19" s="104"/>
       <c r="AZ19" s="105"/>
       <c r="BA19" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB19" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -4045,7 +4047,7 @@
       <c r="L20" s="39"/>
       <c r="M20" s="16"/>
       <c r="N20" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O20" s="19">
@@ -4087,24 +4089,24 @@
         <v>0</v>
       </c>
       <c r="AJ20" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK20" s="94"/>
       <c r="AL20" s="97"/>
       <c r="AM20" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN20" s="48">
         <v>65</v>
       </c>
       <c r="AO20" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP20" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ20" s="51"/>
@@ -4112,11 +4114,11 @@
         <v>0</v>
       </c>
       <c r="AS20" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT20" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU20" s="27"/>
@@ -4126,11 +4128,11 @@
       <c r="AY20" s="104"/>
       <c r="AZ20" s="105"/>
       <c r="BA20" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB20" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -4149,7 +4151,7 @@
       <c r="L21" s="39"/>
       <c r="M21" s="45"/>
       <c r="N21" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O21" s="19">
@@ -4191,24 +4193,24 @@
         <v>0</v>
       </c>
       <c r="AJ21" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK21" s="94"/>
       <c r="AL21" s="97"/>
       <c r="AM21" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN21" s="48">
         <v>65</v>
       </c>
       <c r="AO21" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP21" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ21" s="51"/>
@@ -4216,11 +4218,11 @@
         <v>0</v>
       </c>
       <c r="AS21" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT21" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU21" s="27"/>
@@ -4230,11 +4232,11 @@
       <c r="AY21" s="104"/>
       <c r="AZ21" s="105"/>
       <c r="BA21" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB21" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -4253,7 +4255,7 @@
       <c r="L22" s="39"/>
       <c r="M22" s="16"/>
       <c r="N22" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O22" s="19">
@@ -4295,24 +4297,24 @@
         <v>0</v>
       </c>
       <c r="AJ22" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK22" s="94"/>
       <c r="AL22" s="97"/>
       <c r="AM22" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN22" s="48">
         <v>65</v>
       </c>
       <c r="AO22" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP22" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ22" s="51"/>
@@ -4320,11 +4322,11 @@
         <v>0</v>
       </c>
       <c r="AS22" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT22" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU22" s="27"/>
@@ -4334,11 +4336,11 @@
       <c r="AY22" s="104"/>
       <c r="AZ22" s="105"/>
       <c r="BA22" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB22" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -4357,7 +4359,7 @@
       <c r="L23" s="39"/>
       <c r="M23" s="45"/>
       <c r="N23" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O23" s="19">
@@ -4399,24 +4401,24 @@
         <v>0</v>
       </c>
       <c r="AJ23" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK23" s="94"/>
       <c r="AL23" s="97"/>
       <c r="AM23" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN23" s="48">
         <v>65</v>
       </c>
       <c r="AO23" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP23" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ23" s="51"/>
@@ -4424,11 +4426,11 @@
         <v>0</v>
       </c>
       <c r="AS23" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT23" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU23" s="27"/>
@@ -4438,11 +4440,11 @@
       <c r="AY23" s="104"/>
       <c r="AZ23" s="105"/>
       <c r="BA23" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB23" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -4461,7 +4463,7 @@
       <c r="L24" s="39"/>
       <c r="M24" s="16"/>
       <c r="N24" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O24" s="19">
@@ -4503,24 +4505,24 @@
         <v>0</v>
       </c>
       <c r="AJ24" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK24" s="94"/>
       <c r="AL24" s="97"/>
       <c r="AM24" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN24" s="48">
         <v>65</v>
       </c>
       <c r="AO24" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP24" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ24" s="51"/>
@@ -4528,11 +4530,11 @@
         <v>0</v>
       </c>
       <c r="AS24" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT24" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU24" s="27"/>
@@ -4542,11 +4544,11 @@
       <c r="AY24" s="104"/>
       <c r="AZ24" s="105"/>
       <c r="BA24" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB24" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -4565,7 +4567,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="16"/>
       <c r="N25" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O25" s="19">
@@ -4607,24 +4609,24 @@
         <v>0</v>
       </c>
       <c r="AJ25" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK25" s="94"/>
       <c r="AL25" s="97"/>
       <c r="AM25" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN25" s="48">
         <v>65</v>
       </c>
       <c r="AO25" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP25" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ25" s="51"/>
@@ -4632,11 +4634,11 @@
         <v>0</v>
       </c>
       <c r="AS25" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT25" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU25" s="27"/>
@@ -4646,11 +4648,11 @@
       <c r="AY25" s="104"/>
       <c r="AZ25" s="105"/>
       <c r="BA25" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB25" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -4669,7 +4671,7 @@
       <c r="L26" s="39"/>
       <c r="M26" s="45"/>
       <c r="N26" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O26" s="19">
@@ -4711,24 +4713,24 @@
         <v>0</v>
       </c>
       <c r="AJ26" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK26" s="94"/>
       <c r="AL26" s="97"/>
       <c r="AM26" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN26" s="48">
         <v>65</v>
       </c>
       <c r="AO26" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP26" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ26" s="51"/>
@@ -4736,11 +4738,11 @@
         <v>0</v>
       </c>
       <c r="AS26" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT26" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU26" s="27"/>
@@ -4750,11 +4752,11 @@
       <c r="AY26" s="104"/>
       <c r="AZ26" s="105"/>
       <c r="BA26" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB26" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -4773,7 +4775,7 @@
       <c r="L27" s="39"/>
       <c r="M27" s="45"/>
       <c r="N27" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O27" s="19">
@@ -4815,24 +4817,24 @@
         <v>0</v>
       </c>
       <c r="AJ27" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK27" s="94"/>
       <c r="AL27" s="97"/>
       <c r="AM27" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN27" s="48">
         <v>65</v>
       </c>
       <c r="AO27" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP27" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ27" s="51"/>
@@ -4840,11 +4842,11 @@
         <v>0</v>
       </c>
       <c r="AS27" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT27" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU27" s="27"/>
@@ -4854,11 +4856,11 @@
       <c r="AY27" s="104"/>
       <c r="AZ27" s="105"/>
       <c r="BA27" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB27" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -4877,7 +4879,7 @@
       <c r="L28" s="39"/>
       <c r="M28" s="45"/>
       <c r="N28" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O28" s="19">
@@ -4919,24 +4921,24 @@
         <v>0</v>
       </c>
       <c r="AJ28" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK28" s="94"/>
       <c r="AL28" s="97"/>
       <c r="AM28" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN28" s="48">
         <v>65</v>
       </c>
       <c r="AO28" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP28" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ28" s="51"/>
@@ -4944,11 +4946,11 @@
         <v>0</v>
       </c>
       <c r="AS28" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT28" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU28" s="27"/>
@@ -4958,11 +4960,11 @@
       <c r="AY28" s="104"/>
       <c r="AZ28" s="105"/>
       <c r="BA28" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB28" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -4981,7 +4983,7 @@
       <c r="L29" s="39"/>
       <c r="M29" s="45"/>
       <c r="N29" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O29" s="19">
@@ -5023,24 +5025,24 @@
         <v>0</v>
       </c>
       <c r="AJ29" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK29" s="94"/>
       <c r="AL29" s="97"/>
       <c r="AM29" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN29" s="48">
         <v>65</v>
       </c>
       <c r="AO29" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP29" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ29" s="51"/>
@@ -5048,11 +5050,11 @@
         <v>0</v>
       </c>
       <c r="AS29" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT29" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU29" s="27"/>
@@ -5062,11 +5064,11 @@
       <c r="AY29" s="104"/>
       <c r="AZ29" s="105"/>
       <c r="BA29" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB29" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -5085,7 +5087,7 @@
       <c r="L30" s="39"/>
       <c r="M30" s="16"/>
       <c r="N30" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O30" s="19">
@@ -5127,24 +5129,24 @@
         <v>0</v>
       </c>
       <c r="AJ30" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK30" s="94"/>
       <c r="AL30" s="97"/>
       <c r="AM30" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN30" s="48">
         <v>65</v>
       </c>
       <c r="AO30" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP30" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ30" s="51"/>
@@ -5152,11 +5154,11 @@
         <v>0</v>
       </c>
       <c r="AS30" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT30" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU30" s="27"/>
@@ -5166,11 +5168,11 @@
       <c r="AY30" s="104"/>
       <c r="AZ30" s="105"/>
       <c r="BA30" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB30" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -5189,7 +5191,7 @@
       <c r="L31" s="39"/>
       <c r="M31" s="45"/>
       <c r="N31" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O31" s="19">
@@ -5231,24 +5233,24 @@
         <v>0</v>
       </c>
       <c r="AJ31" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK31" s="95"/>
       <c r="AL31" s="97"/>
       <c r="AM31" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN31" s="48">
         <v>65</v>
       </c>
       <c r="AO31" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP31" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ31" s="51"/>
@@ -5256,11 +5258,11 @@
         <v>0</v>
       </c>
       <c r="AS31" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT31" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU31" s="27"/>
@@ -5270,11 +5272,11 @@
       <c r="AY31" s="104"/>
       <c r="AZ31" s="105"/>
       <c r="BA31" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB31" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -5293,7 +5295,7 @@
       <c r="L32" s="39"/>
       <c r="M32" s="45"/>
       <c r="N32" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O32" s="19">
@@ -5335,34 +5337,34 @@
         <v>0</v>
       </c>
       <c r="AJ32" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK32" s="94"/>
       <c r="AL32" s="97"/>
       <c r="AM32" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN32" s="48">
         <v>65</v>
       </c>
       <c r="AO32" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP32" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ32" s="51"/>
       <c r="AR32" s="35"/>
       <c r="AS32" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT32" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU32" s="27"/>
@@ -5372,11 +5374,11 @@
       <c r="AY32" s="104"/>
       <c r="AZ32" s="105"/>
       <c r="BA32" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB32" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -5395,7 +5397,7 @@
       <c r="L33" s="39"/>
       <c r="M33" s="45"/>
       <c r="N33" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O33" s="19">
@@ -5437,24 +5439,24 @@
         <v>0</v>
       </c>
       <c r="AJ33" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK33" s="94"/>
       <c r="AL33" s="97"/>
       <c r="AM33" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN33" s="48">
         <v>65</v>
       </c>
       <c r="AO33" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP33" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ33" s="51"/>
@@ -5462,11 +5464,11 @@
         <v>0</v>
       </c>
       <c r="AS33" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT33" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU33" s="27"/>
@@ -5476,11 +5478,11 @@
       <c r="AY33" s="104"/>
       <c r="AZ33" s="105"/>
       <c r="BA33" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB33" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -5499,7 +5501,7 @@
       <c r="L34" s="39"/>
       <c r="M34" s="45"/>
       <c r="N34" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O34" s="19">
@@ -5541,24 +5543,24 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK34" s="94"/>
       <c r="AL34" s="97"/>
       <c r="AM34" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN34" s="48">
         <v>65</v>
       </c>
       <c r="AO34" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP34" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ34" s="51"/>
@@ -5566,11 +5568,11 @@
         <v>0</v>
       </c>
       <c r="AS34" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT34" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU34" s="27"/>
@@ -5580,11 +5582,11 @@
       <c r="AY34" s="104"/>
       <c r="AZ34" s="105"/>
       <c r="BA34" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB34" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -5603,7 +5605,7 @@
       <c r="L35" s="39"/>
       <c r="M35" s="45"/>
       <c r="N35" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O35" s="19">
@@ -5645,24 +5647,24 @@
         <v>0</v>
       </c>
       <c r="AJ35" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK35" s="94"/>
       <c r="AL35" s="97"/>
       <c r="AM35" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN35" s="48">
         <v>65</v>
       </c>
       <c r="AO35" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP35" s="50" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AQ35" s="51"/>
@@ -5670,11 +5672,11 @@
         <v>0</v>
       </c>
       <c r="AS35" s="36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AT35" s="26" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AU35" s="27"/>
@@ -5684,11 +5686,11 @@
       <c r="AY35" s="104"/>
       <c r="AZ35" s="105"/>
       <c r="BA35" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB35" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -5707,7 +5709,7 @@
       <c r="L36" s="39"/>
       <c r="M36" s="45"/>
       <c r="N36" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O36" s="19">
@@ -5749,20 +5751,20 @@
         <v>0</v>
       </c>
       <c r="AJ36" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK36" s="94"/>
       <c r="AL36" s="97"/>
       <c r="AM36" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN36" s="48">
         <v>65</v>
       </c>
       <c r="AO36" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP36" s="50"/>
@@ -5777,11 +5779,11 @@
       <c r="AY36" s="104"/>
       <c r="AZ36" s="105"/>
       <c r="BA36" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB36" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -5800,7 +5802,7 @@
       <c r="L37" s="39"/>
       <c r="M37" s="45"/>
       <c r="N37" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O37" s="19">
@@ -5842,20 +5844,20 @@
         <v>0</v>
       </c>
       <c r="AJ37" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK37" s="94"/>
       <c r="AL37" s="97"/>
       <c r="AM37" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN37" s="48">
         <v>65</v>
       </c>
       <c r="AO37" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP37" s="50" t="e">
@@ -5881,11 +5883,11 @@
       <c r="AY37" s="104"/>
       <c r="AZ37" s="105"/>
       <c r="BA37" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB37" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -5904,7 +5906,7 @@
       <c r="L38" s="39"/>
       <c r="M38" s="40"/>
       <c r="N38" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O38" s="47">
@@ -5946,20 +5948,20 @@
         <v>0</v>
       </c>
       <c r="AJ38" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK38" s="94"/>
       <c r="AL38" s="97"/>
       <c r="AM38" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN38" s="48">
         <v>65</v>
       </c>
       <c r="AO38" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP38" s="50" t="e">
@@ -5985,11 +5987,11 @@
       <c r="AY38" s="104"/>
       <c r="AZ38" s="105"/>
       <c r="BA38" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB38" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -6008,7 +6010,7 @@
       <c r="L39" s="39"/>
       <c r="M39" s="45"/>
       <c r="N39" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O39" s="19">
@@ -6050,20 +6052,20 @@
         <v>0</v>
       </c>
       <c r="AJ39" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK39" s="94"/>
       <c r="AL39" s="97"/>
       <c r="AM39" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN39" s="48">
         <v>65</v>
       </c>
       <c r="AO39" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP39" s="50" t="e">
@@ -6089,11 +6091,11 @@
       <c r="AY39" s="104"/>
       <c r="AZ39" s="105"/>
       <c r="BA39" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB39" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -6112,7 +6114,7 @@
       <c r="L40" s="39"/>
       <c r="M40" s="45"/>
       <c r="N40" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O40" s="19">
@@ -6154,20 +6156,20 @@
         <v>0</v>
       </c>
       <c r="AJ40" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK40" s="94"/>
       <c r="AL40" s="97"/>
       <c r="AM40" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN40" s="48">
         <v>65</v>
       </c>
       <c r="AO40" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP40" s="50"/>
@@ -6182,11 +6184,11 @@
       <c r="AY40" s="104"/>
       <c r="AZ40" s="105"/>
       <c r="BA40" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB40" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -6205,7 +6207,7 @@
       <c r="L41" s="39"/>
       <c r="M41" s="45"/>
       <c r="N41" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O41" s="19">
@@ -6247,20 +6249,20 @@
         <v>0</v>
       </c>
       <c r="AJ41" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK41" s="94"/>
       <c r="AL41" s="97"/>
       <c r="AM41" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN41" s="48">
         <v>65</v>
       </c>
       <c r="AO41" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP41" s="50" t="e">
@@ -6286,11 +6288,11 @@
       <c r="AY41" s="104"/>
       <c r="AZ41" s="105"/>
       <c r="BA41" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB41" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -6309,7 +6311,7 @@
       <c r="L42" s="39"/>
       <c r="M42" s="45"/>
       <c r="N42" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O42" s="47">
@@ -6351,20 +6353,20 @@
         <v>0</v>
       </c>
       <c r="AJ42" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK42" s="94"/>
       <c r="AL42" s="97"/>
       <c r="AM42" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN42" s="48">
         <v>65</v>
       </c>
       <c r="AO42" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP42" s="50" t="e">
@@ -6390,11 +6392,11 @@
       <c r="AY42" s="104"/>
       <c r="AZ42" s="105"/>
       <c r="BA42" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB42" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -6413,7 +6415,7 @@
       <c r="L43" s="39"/>
       <c r="M43" s="45"/>
       <c r="N43" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O43" s="19">
@@ -6455,20 +6457,20 @@
         <v>0</v>
       </c>
       <c r="AJ43" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK43" s="94"/>
       <c r="AL43" s="97"/>
       <c r="AM43" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN43" s="48">
         <v>65</v>
       </c>
       <c r="AO43" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP43" s="50" t="e">
@@ -6494,11 +6496,11 @@
       <c r="AY43" s="104"/>
       <c r="AZ43" s="105"/>
       <c r="BA43" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB43" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -6517,7 +6519,7 @@
       <c r="L44" s="39"/>
       <c r="M44" s="45"/>
       <c r="N44" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O44" s="19">
@@ -6556,18 +6558,18 @@
         <v>0</v>
       </c>
       <c r="AJ44" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK44" s="94"/>
       <c r="AL44" s="97"/>
       <c r="AM44" s="34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN44" s="48"/>
       <c r="AO44" s="49">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AP44" s="50"/>
@@ -6582,11 +6584,11 @@
       <c r="AY44" s="104"/>
       <c r="AZ44" s="105"/>
       <c r="BA44" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB44" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -6605,7 +6607,7 @@
       <c r="L45" s="39"/>
       <c r="M45" s="45"/>
       <c r="N45" s="18">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O45" s="19">
@@ -6647,20 +6649,20 @@
         <v>0</v>
       </c>
       <c r="AJ45" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK45" s="94"/>
       <c r="AL45" s="97"/>
       <c r="AM45" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN45" s="48">
         <v>65</v>
       </c>
       <c r="AO45" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP45" s="50" t="e">
@@ -6686,11 +6688,11 @@
       <c r="AY45" s="104"/>
       <c r="AZ45" s="105"/>
       <c r="BA45" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB45" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -6709,7 +6711,7 @@
       <c r="L46" s="39"/>
       <c r="M46" s="45"/>
       <c r="N46" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O46" s="47">
@@ -6751,20 +6753,20 @@
         <v>0</v>
       </c>
       <c r="AJ46" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK46" s="94"/>
       <c r="AL46" s="97"/>
       <c r="AM46" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN46" s="48">
         <v>65</v>
       </c>
       <c r="AO46" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP46" s="50" t="e">
@@ -6790,11 +6792,11 @@
       <c r="AY46" s="104"/>
       <c r="AZ46" s="105"/>
       <c r="BA46" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB46" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -6813,7 +6815,7 @@
       <c r="L47" s="39"/>
       <c r="M47" s="45"/>
       <c r="N47" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O47" s="47">
@@ -6855,20 +6857,20 @@
         <v>0</v>
       </c>
       <c r="AJ47" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK47" s="94"/>
       <c r="AL47" s="97"/>
       <c r="AM47" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN47" s="48">
         <v>65</v>
       </c>
       <c r="AO47" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP47" s="50" t="e">
@@ -6894,11 +6896,11 @@
       <c r="AY47" s="104"/>
       <c r="AZ47" s="105"/>
       <c r="BA47" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB47" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -6917,7 +6919,7 @@
       <c r="L48" s="39"/>
       <c r="M48" s="45"/>
       <c r="N48" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O48" s="47">
@@ -6959,20 +6961,20 @@
         <v>0</v>
       </c>
       <c r="AJ48" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK48" s="95"/>
       <c r="AL48" s="97"/>
       <c r="AM48" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN48" s="48">
         <v>65</v>
       </c>
       <c r="AO48" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP48" s="50" t="e">
@@ -6998,11 +7000,11 @@
       <c r="AY48" s="104"/>
       <c r="AZ48" s="105"/>
       <c r="BA48" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB48" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -7021,7 +7023,7 @@
       <c r="L49" s="39"/>
       <c r="M49" s="45"/>
       <c r="N49" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O49" s="47">
@@ -7063,20 +7065,20 @@
         <v>0</v>
       </c>
       <c r="AJ49" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK49" s="94"/>
       <c r="AL49" s="97"/>
       <c r="AM49" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN49" s="48">
         <v>65</v>
       </c>
       <c r="AO49" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP49" s="50" t="e">
@@ -7102,11 +7104,11 @@
       <c r="AY49" s="104"/>
       <c r="AZ49" s="105"/>
       <c r="BA49" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB49" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -7125,7 +7127,7 @@
       <c r="L50" s="39"/>
       <c r="M50" s="45"/>
       <c r="N50" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O50" s="47">
@@ -7167,20 +7169,20 @@
         <v>0</v>
       </c>
       <c r="AJ50" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK50" s="94"/>
       <c r="AL50" s="97"/>
       <c r="AM50" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN50" s="48">
         <v>65</v>
       </c>
       <c r="AO50" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP50" s="50" t="e">
@@ -7206,11 +7208,11 @@
       <c r="AY50" s="104"/>
       <c r="AZ50" s="105"/>
       <c r="BA50" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB50" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -7229,7 +7231,7 @@
       <c r="L51" s="39"/>
       <c r="M51" s="45"/>
       <c r="N51" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O51" s="47">
@@ -7271,20 +7273,20 @@
         <v>0</v>
       </c>
       <c r="AJ51" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK51" s="94"/>
       <c r="AL51" s="97"/>
       <c r="AM51" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN51" s="48">
         <v>65</v>
       </c>
       <c r="AO51" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP51" s="50" t="e">
@@ -7310,11 +7312,11 @@
       <c r="AY51" s="104"/>
       <c r="AZ51" s="105"/>
       <c r="BA51" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB51" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -7333,7 +7335,7 @@
       <c r="L52" s="39"/>
       <c r="M52" s="45"/>
       <c r="N52" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O52" s="47">
@@ -7375,20 +7377,20 @@
         <v>0</v>
       </c>
       <c r="AJ52" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK52" s="95"/>
       <c r="AL52" s="97"/>
       <c r="AM52" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN52" s="48">
         <v>65</v>
       </c>
       <c r="AO52" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP52" s="50" t="e">
@@ -7414,11 +7416,11 @@
       <c r="AY52" s="104"/>
       <c r="AZ52" s="105"/>
       <c r="BA52" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB52" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -7437,7 +7439,7 @@
       <c r="L53" s="39"/>
       <c r="M53" s="40"/>
       <c r="N53" s="41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O53" s="47">
@@ -7479,20 +7481,20 @@
         <v>0</v>
       </c>
       <c r="AJ53" s="92">
-        <f t="shared" si="14"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK53" s="96"/>
       <c r="AL53" s="98"/>
       <c r="AM53" s="34" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AN53" s="48">
         <v>65</v>
       </c>
       <c r="AO53" s="49" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AP53" s="50" t="e">
@@ -7518,16 +7520,34 @@
       <c r="AY53" s="104"/>
       <c r="AZ53" s="105"/>
       <c r="BA53" s="105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB53" s="106">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="N1:AB1"/>
+    <mergeCell ref="U2:Z2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:U3"/>
+    <mergeCell ref="W3:AB3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="P2:S2"/>
     <mergeCell ref="AD1:AK2"/>
     <mergeCell ref="BB3:BB4"/>
     <mergeCell ref="AU3:AU4"/>
@@ -7543,24 +7563,6 @@
     <mergeCell ref="BA3:BA4"/>
     <mergeCell ref="AT3:AT4"/>
     <mergeCell ref="AD3:AJ3"/>
-    <mergeCell ref="U2:Z2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:U3"/>
-    <mergeCell ref="W3:AB3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="N1:AB1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
